--- a/data/Historico.xlsx
+++ b/data/Historico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -715,7 +715,7 @@
         <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>13</v>
@@ -758,6 +758,366 @@
       </c>
       <c r="J9" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>014005ed-c069-4e0e-b1df-25b3c996ef74</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DANTE HERRERA</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45990.32777777778</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45990.75277777778</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>636d0bee-bf98-4cc9-ab35-d6bb4c7e7fd0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45990.33333333334</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>45990.83333333334</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>84486179-476e-4155-8ed1-5fb9d1f83173</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45990.33333333334</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>45991.20833333334</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>daf27586-4c9b-4c2c-8b5a-e9eb8fc85238</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45990.33333333334</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>45991.29166666666</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>693a9c5a-e188-41cf-9668-367072276cde</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46111.33333333334</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0c0ff5cc-67a4-4bbc-8f89-3c6e2bf212d7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VANESA</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46112.33333333334</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46112.70833333334</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>be3af50d-4a89-43c1-9516-3106afe03da2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46114.33333333334</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46114.97916666666</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8010c274-e391-4b91-a627-7d7fd42ec2db</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46111.33333333334</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>44185304-38ac-4e5e-9fba-f4f2fb94a327</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VANESA</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46112.33333333334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46112.70833333334</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>a8f8964a-c1f0-4505-bb6d-4159bcb77417</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46114.33333333334</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46114.97916666666</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico.xlsx
+++ b/data/Historico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,20 +453,30 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>VALOR_HS_JORNAL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IMPORTE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>HORAS_TRABAJADAS</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HORAS_NORMALES_DIURNAS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>HORAS_EXTRAS_NORMALES</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HORAS_NOCTURNAS</t>
         </is>
@@ -496,10 +506,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>10.2</v>
+        <v>12000</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="I2" t="n">
         <v>10.2</v>
@@ -507,6 +517,12 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
+      <c r="K2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,10 +548,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
@@ -543,6 +559,12 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
+      <c r="K3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,15 +590,21 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>355000</v>
+      </c>
+      <c r="I4" t="n">
         <v>21</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -604,15 +632,21 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>390000</v>
+      </c>
+      <c r="I5" t="n">
         <v>23</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -640,10 +674,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>10.2</v>
+        <v>12000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="I6" t="n">
         <v>10.2</v>
@@ -651,6 +685,12 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="K6" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,10 +716,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="I7" t="n">
         <v>12</v>
@@ -687,6 +727,12 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -696,7 +742,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -712,15 +758,21 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>455000</v>
+      </c>
+      <c r="I8" t="n">
         <v>21</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>13</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -748,15 +800,21 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>390000</v>
+      </c>
+      <c r="I9" t="n">
         <v>23</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>14</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -784,10 +842,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>10.2</v>
+        <v>12000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="I10" t="n">
         <v>10.2</v>
@@ -795,6 +853,12 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
+      <c r="K10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -820,10 +884,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="I11" t="n">
         <v>12</v>
@@ -831,6 +895,12 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -856,15 +926,21 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>355000</v>
+      </c>
+      <c r="I12" t="n">
         <v>21</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>13</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>8</v>
       </c>
     </row>
@@ -892,15 +968,21 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>390000</v>
+      </c>
+      <c r="I13" t="n">
         <v>23</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>14</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -928,15 +1010,21 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I14" t="n">
         <v>12</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -964,15 +1052,21 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H15" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I15" t="n">
         <v>9</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>7</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1000,15 +1094,21 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>102500</v>
+      </c>
+      <c r="I16" t="n">
         <v>15.5</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>8</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1036,15 +1136,21 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I17" t="n">
         <v>12</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1072,15 +1178,21 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H18" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I18" t="n">
         <v>9</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>7</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1108,16 +1220,152 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>102500</v>
+      </c>
+      <c r="I19" t="n">
         <v>15.5</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>8</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7d790afd-b98e-4fd1-8eb8-ce79e7d6b476</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46118.33333333334</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46118.70833333334</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>66a757b9-11bd-4e43-8a76-c78e038137f8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46118.33333333334</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46118.66666666666</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7c299bd1-84e6-4bb4-9340-828b0db484c7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46118.33333333334</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46118.66666666666</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>aaaa</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico.xlsx
+++ b/data/Historico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO_CONFIRMADO</t>
+          <t>ELIMINADO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1365,6 +1365,178 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fcb5e822-760e-433e-ba7c-959657135f84</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46111.33333333334</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6da7e4d7-354b-4480-b8e8-fe0d27c59b22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VANESA</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46112.33333333334</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46112.70833333334</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H24" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>70482157-87f3-4e22-b8cb-725d01d3dd0b</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ELIMINADO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46114.33333333334</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46114.97916666666</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>102500</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2b7625ff-4012-4124-98e8-62b3050c2c92</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DANTE HERRERA</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46118.33333333334</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46118.70833333334</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>108000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Historico.xlsx
+++ b/data/Historico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,12 +473,27 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>HORAS_EXTRAS_NORMALES</t>
+          <t>HORAS_NORMALES_NOCTURNAS</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HORAS_NOCTURNAS</t>
+          <t>HORAS_EXTRAS_DIURNAS</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>HORAS_EXTRAS_NOCTURNAS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>HORAS_EXTRAS_DIURNAS_FERIADO</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>HORAS_EXTRAS_NOCTURNAS_FERIADO</t>
         </is>
       </c>
     </row>
@@ -518,9 +533,18 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>10.2</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -560,9 +584,18 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -602,10 +635,19 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
         <v>13</v>
       </c>
-      <c r="L4" t="n">
-        <v>8</v>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -644,10 +686,19 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
         <v>14</v>
       </c>
-      <c r="L5" t="n">
-        <v>9</v>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -686,9 +737,18 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>10.2</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -728,9 +788,18 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,10 +839,19 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
         <v>13</v>
       </c>
-      <c r="L8" t="n">
-        <v>8</v>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -812,10 +890,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
         <v>14</v>
       </c>
-      <c r="L9" t="n">
-        <v>9</v>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -854,9 +941,18 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>10.2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -896,9 +992,18 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>12</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -938,10 +1043,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
         <v>13</v>
       </c>
-      <c r="L12" t="n">
-        <v>8</v>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -980,10 +1094,19 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="n">
         <v>14</v>
       </c>
-      <c r="L13" t="n">
-        <v>9</v>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1022,9 +1145,18 @@
         <v>8</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1064,9 +1196,18 @@
         <v>7</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1106,10 +1247,19 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L16" t="n">
         <v>5</v>
       </c>
-      <c r="L16" t="n">
-        <v>2.5</v>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1148,9 +1298,18 @@
         <v>8</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1190,9 +1349,18 @@
         <v>7</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1232,10 +1400,19 @@
         <v>8</v>
       </c>
       <c r="K19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="L19" t="n">
-        <v>2.5</v>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1274,9 +1451,18 @@
         <v>8</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1321,6 +1507,15 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1365,6 +1560,15 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1404,9 +1608,18 @@
         <v>8</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,9 +1659,18 @@
         <v>7</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1488,10 +1710,19 @@
         <v>8</v>
       </c>
       <c r="K25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" t="n">
-        <v>2.5</v>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1538,6 +1769,321 @@
       </c>
       <c r="L26" t="n">
         <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ad6c9bf9-2f98-4796-bb9a-4b23be63bda7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46117.91666666666</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46118.16666666666</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>df1bf760-e4fc-4316-9447-49a4d3e69d76</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46117.91666666666</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46118.16666666666</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>93818431-43fb-4428-afe1-3d52a9ebb6af</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46117.08333333334</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46117.95833333334</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>185000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>21</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>15</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ee87b005-b262-4c8c-b35e-269da47055b6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46117.08333333334</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46117.95833333334</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>210000</v>
+      </c>
+      <c r="I30" t="n">
+        <v>21</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>21</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5601dfac-2802-4ecc-ad49-0632c7acc67a</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46117.91666666666</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46118.25</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>c2457cee-dc75-46bd-8ace-fdd3b6662ed5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NO_CONFIRMADO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DANTE HERRERA</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46117.91666666666</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46118.25</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>132796.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
